--- a/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -80,6 +80,9 @@
     <t xml:space="preserve">Acetobacteraceae</t>
   </si>
   <si>
+    <t xml:space="preserve">Acetobacter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acetobacter thailandicus</t>
   </si>
   <si>
@@ -87,6 +90,9 @@
   </si>
   <si>
     <t xml:space="preserve">Erwiniaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tatumella</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_338</t>
@@ -558,15 +564,15 @@
         <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -581,10 +587,10 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -592,7 +598,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -607,18 +613,18 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -633,10 +639,10 @@
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -644,7 +650,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -656,13 +662,13 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -670,7 +676,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -696,7 +702,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -711,10 +717,10 @@
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -722,7 +728,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -748,7 +754,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -766,7 +772,7 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>

--- a/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -68,6 +68,9 @@
     <t xml:space="preserve">Enterobacterales</t>
   </si>
   <si>
+    <t xml:space="preserve">Erwiniaceae</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
     <t xml:space="preserve">Cluster_337</t>
   </si>
   <si>
-    <t xml:space="preserve">Erwiniaceae</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tatumella</t>
   </si>
   <si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t xml:space="preserve">Gluconobacter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cerinus</t>
   </si>
 </sst>
 </file>
@@ -535,7 +538,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -546,7 +549,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -555,24 +558,24 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -587,7 +590,7 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -639,7 +642,7 @@
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
         <v>32</v>
@@ -717,7 +720,7 @@
         <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
@@ -763,19 +766,19 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" t="s">
         <v>41</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Gluconobacter</t>
   </si>
   <si>
-    <t xml:space="preserve">cerinus</t>
+    <t xml:space="preserve">Gluconobacter cerinus</t>
   </si>
 </sst>
 </file>

--- a/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_2/ps_rare_16S_D2_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -38,28 +38,88 @@
     <t xml:space="preserve">Species</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pseudomonadota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gammaproteobacteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burkholderiales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burkholderiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robbsia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alphaproteobacteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acetobacterales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acetobacteraceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gluconobacter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_113</t>
   </si>
   <si>
-    <t xml:space="preserve">Bacteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pseudomonadota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gammaproteobacteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burkholderiales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oxalobacteraceae</t>
   </si>
   <si>
     <t xml:space="preserve">Massilia</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
+    <t xml:space="preserve">Cluster_1389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacilli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacillales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planococcaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lactobacillales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lactobacillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levilactobacillus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lactobacillus brevis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_1533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lysinibacillus</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_16</t>
@@ -74,73 +134,145 @@
     <t xml:space="preserve">Cluster_20</t>
   </si>
   <si>
-    <t xml:space="preserve">Alphaproteobacteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acetobacterales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acetobacteraceae</t>
-  </si>
-  <si>
     <t xml:space="preserve">Acetobacter</t>
   </si>
   <si>
     <t xml:space="preserve">Acetobacter thailandicus</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paenibacillales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paenibacillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paenibacillus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pseudomonadales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moraxellaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacillaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacillus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacillus acidicola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neokomagataea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actinomycetota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actinobacteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitasatosporales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streptomycetaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Streptomyces</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_337</t>
   </si>
   <si>
     <t xml:space="preserve">Tatumella</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yersiniaceae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serratia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Serratia symbiotica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phaseolibacter</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_35</t>
   </si>
   <si>
-    <t xml:space="preserve">Pseudomonadales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pseudomonadaceae</t>
   </si>
   <si>
     <t xml:space="preserve">Pseudomonas</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acinetobacter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_449</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_47</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_5</t>
   </si>
   <si>
+    <t xml:space="preserve">Cluster_516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orbaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_53</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cluster_55</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_6</t>
   </si>
   <si>
-    <t xml:space="preserve">Gluconobacter</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gluconobacter cerinus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonadales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonadaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sphingomonas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shouchella</t>
   </si>
 </sst>
 </file>
@@ -532,16 +664,16 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -549,7 +681,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -558,10 +690,10 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>22</v>
@@ -570,30 +702,30 @@
         <v>23</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -601,51 +733,51 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -653,7 +785,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -665,13 +797,13 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -679,7 +811,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -688,24 +820,24 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -717,13 +849,13 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -731,25 +863,25 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -757,28 +889,496 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" t="s">
+        <v>64</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" t="s">
+        <v>53</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s">
         <v>40</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" t="s">
         <v>41</v>
       </c>
-      <c r="H12" t="s">
-        <v>42</v>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
